--- a/sampleprojects/CorporateTax/excel/states/OR_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/OR_corp.xlsx
@@ -166,31 +166,31 @@
     <t>Is financial institution; Is financial institution subject to 7.6% rate</t>
   </si>
   <si>
-    <t>result.or_is_financial_institution == true</t>
+    <t>or_result.is_financial_institution == true</t>
   </si>
   <si>
     <t>Calculate OR tax for financial institutions (7.6% rate); Financial institutions use 7.6% rate instead of 6.6%</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = apportionment.state_taxable_income * result.or_financial_institution_rate; set apportionment.state_tax = the maximum of (apportionment.state_tax) and (result.or_minimum_tax); set apportionment.state_tax = the maximum of (apportionment.state_tax - apportionment.state_credits) and (result.or_minimum_tax); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>set apportionment.state_tax = apportionment.state_taxable_income * or_result.financial_institution_rate; set apportionment.state_tax = the maximum of (apportionment.state_tax) and (or_result.minimum_tax); set apportionment.state_tax = the maximum of (apportionment.state_tax - apportionment.state_credits) and (or_result.minimum_tax); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>Calculate OR tax for regular corporations (6.6% rate); Regular corporations use 6.6% flat rate</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = apportionment.state_taxable_income * apportionment.state_tax_rate; set apportionment.state_tax = the maximum of (apportionment.state_tax) and (result.or_minimum_tax); set apportionment.state_tax = the maximum of (apportionment.state_tax - apportionment.state_credits) and (result.or_minimum_tax); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>set apportionment.state_tax = apportionment.state_taxable_income * apportionment.state_tax_rate; set apportionment.state_tax = the maximum of (apportionment.state_tax) and (or_result.minimum_tax); set apportionment.state_tax = the maximum of (apportionment.state_tax - apportionment.state_credits) and (or_result.minimum_tax); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>No nexus - no tax liability; No nexus - no tax liability</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = 0.0; set result.or_minimum_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
+    <t>set apportionment.state_tax = 0.0; set or_result.minimum_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
   </si>
   <si>
     <t>Nexus but no taxable income (still owe minimum tax!); No excise tax, but MINIMUM TAX STILL APPLIES</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = result.or_minimum_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>set apportionment.state_tax = or_result.minimum_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>OR corporate excise tax (FINANCIAL INSTITUTIONS)</t>
@@ -247,13 +247,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
+    <t>or_apportionment</t>
   </si>
   <si>
     <t>(3 attributes)</t>
   </si>
   <si>
-    <t>or_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>double</t>
@@ -268,7 +268,7 @@
     <t>OR economic nexus threshold: $750,000 in Oregon sales (higher than typical)</t>
   </si>
   <si>
-    <t>or_state_tax_rate</t>
+    <t>state_tax_rate</t>
   </si>
   <si>
     <t>0.066</t>
@@ -277,7 +277,7 @@
     <t>OR corporate excise tax rate: 6.6% flat rate (7.6% for financial institutions) - ORS 317.061</t>
   </si>
   <si>
-    <t>or_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
@@ -289,13 +289,13 @@
     <t>OR economic nexus transaction count threshold: 200 transactions</t>
   </si>
   <si>
-    <t>result</t>
+    <t>or_result</t>
   </si>
   <si>
     <t>(4 attributes)</t>
   </si>
   <si>
-    <t>or_financial_institution_rate</t>
+    <t>financial_institution_rate</t>
   </si>
   <si>
     <t>0.076</t>
@@ -304,7 +304,7 @@
     <t>OR tax rate for financial institutions: 7.6% - ORS 317.061(2)</t>
   </si>
   <si>
-    <t>or_is_financial_institution</t>
+    <t>is_financial_institution</t>
   </si>
   <si>
     <t>boolean</t>
@@ -316,7 +316,7 @@
     <t>Is financial institution subject to 7.6% rate instead of 6.6%</t>
   </si>
   <si>
-    <t>or_minimum_tax</t>
+    <t>minimum_tax</t>
   </si>
   <si>
     <t>150.0</t>
@@ -325,7 +325,7 @@
     <t>OR minimum excise tax based on Oregon sales - ORS 317.090</t>
   </si>
   <si>
-    <t>or_sales_in_oregon</t>
+    <t>sales_in_oregon</t>
   </si>
   <si>
     <t>0.0</t>
